--- a/BMP_Tutors_Google_Docs_Charts_Companion.xlsx
+++ b/BMP_Tutors_Google_Docs_Charts_Companion.xlsx
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>107716</v>
+        <v>107723</v>
       </c>
       <c r="D23" t="n">
         <v>100</v>
